--- a/cuadros/MAYO/IPSFA.xlsx
+++ b/cuadros/MAYO/IPSFA.xlsx
@@ -1,42 +1,115 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t>SUCURSAL</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>FACTURA</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>TIPO FISCALIZACIÓN</t>
+  </si>
+  <si>
+    <t>RESPONSABLE</t>
+  </si>
+  <si>
+    <t>INCIDENCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE ERROR</t>
+  </si>
+  <si>
+    <t>OBSERVACIÓN</t>
+  </si>
+  <si>
+    <t>MONTO $</t>
+  </si>
+  <si>
+    <t>F COBRADA</t>
+  </si>
+  <si>
+    <t>CLASIFICACIÓN MONTO</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>IPSFA</t>
+  </si>
+  <si>
+    <t>YEFFERSON MAY MORGADO CHACON</t>
+  </si>
+  <si>
+    <t>125981</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>RECEPCION</t>
+  </si>
+  <si>
+    <t>LISBETH SANCHEZ</t>
+  </si>
+  <si>
+    <t>ERROR DE KG EN TARA.</t>
+  </si>
+  <si>
+    <t>TIPO C</t>
+  </si>
+  <si>
+    <t>ERROR DE TARA EN FISCALIZACION</t>
+  </si>
+  <si>
+    <t>SIN_FOTO</t>
+  </si>
+  <si>
+    <t>NINGUNA</t>
+  </si>
+  <si>
+    <t>HIST_20260504164252</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,82 +124,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -414,142 +419,90 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>SUCURSAL</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>FACTURA</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>TIPO DE FISCALIZACION</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>TIPO DE ERROR</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>F COBRADA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HIST_20260501_0</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IPSFA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>adolfo</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4522</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>RECEPCION</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>OMAR LOPEZ</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>TIPO D</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>cobro de 20</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="1" t="n">
-        <v>52</v>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/IPSFA.xlsx
+++ b/cuadros/MAYO/IPSFA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -55,6 +55,9 @@
     <t>ID</t>
   </si>
   <si>
+    <t>FOTO_INCIDENCIA</t>
+  </si>
+  <si>
     <t>IPSFA</t>
   </si>
   <si>
@@ -64,7 +67,7 @@
     <t>125981</t>
   </si>
   <si>
-    <t>2026-05-01</t>
+    <t>2026-05-05</t>
   </si>
   <si>
     <t>RECEPCION</t>
@@ -79,7 +82,7 @@
     <t>TIPO C</t>
   </si>
   <si>
-    <t>ERROR DE TARA EN FISCALIZACION</t>
+    <t>error en tara se coloco 26.6kg la tara y realmente era 23.6kg</t>
   </si>
   <si>
     <t>SIN_FOTO</t>
@@ -420,10 +423,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -463,46 +466,49 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/IPSFA.xlsx
+++ b/cuadros/MAYO/IPSFA.xlsx
@@ -1,115 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
-  <si>
-    <t>SUCURSAL</t>
-  </si>
-  <si>
-    <t>PROVEEDOR</t>
-  </si>
-  <si>
-    <t>FACTURA</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>TIPO FISCALIZACIÓN</t>
-  </si>
-  <si>
-    <t>RESPONSABLE</t>
-  </si>
-  <si>
-    <t>INCIDENCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE ERROR</t>
-  </si>
-  <si>
-    <t>OBSERVACIÓN</t>
-  </si>
-  <si>
-    <t>MONTO $</t>
-  </si>
-  <si>
-    <t>F COBRADA</t>
-  </si>
-  <si>
-    <t>CLASIFICACIÓN MONTO</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>FOTO_INCIDENCIA</t>
-  </si>
-  <si>
-    <t>IPSFA</t>
-  </si>
-  <si>
-    <t>YEFFERSON MAY MORGADO CHACON</t>
-  </si>
-  <si>
-    <t>125981</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>RECEPCION</t>
-  </si>
-  <si>
-    <t>LISBETH SANCHEZ</t>
-  </si>
-  <si>
-    <t>ERROR DE KG EN TARA.</t>
-  </si>
-  <si>
-    <t>TIPO C</t>
-  </si>
-  <si>
-    <t>error en tara se coloco 26.6kg la tara y realmente era 23.6kg</t>
-  </si>
-  <si>
-    <t>SIN_FOTO</t>
-  </si>
-  <si>
-    <t>NINGUNA</t>
-  </si>
-  <si>
-    <t>HIST_20260504164252</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -128,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -422,93 +407,275 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SUCURSAL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TIPO FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>INCIDENCIA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TIPO DE ERROR</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OBSERVACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MONTO $</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>F COBRADA</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CLASIFICACIÓN MONTO</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>FOTO_INCIDENCIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>YEFFERSON MAY MORGADO CHACON</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>125981</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>LISBETH SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>error en tara se coloco 26.6kg la tara y realmente era 23.6kg</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>HIST_20260504164252</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CORPORACION JSL, C.A</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>40097731</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Miguel A. Blanco</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PAN CRUSTISSIMO INTEGRAL 9GRANOS 550GR SE AGREGO DOS VECES</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ID_20260505142248</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>YEFFERSON MAY MORGADO CHACON</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>126062</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ricardo A. Ruiz</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>FALTO POR FISCALIZAR UN PESAJE DE PAPAYA 44.8 KG</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260505144724</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/IPSFA.xlsx
+++ b/cuadros/MAYO/IPSFA.xlsx
@@ -1,12 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +550,7 @@
           <t>HIST_20260504164252</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -612,6 +614,7 @@
           <t>ID_20260505142248</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -624,10 +627,8 @@
           <t>YEFFERSON MAY MORGADO CHACON</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>126062</t>
-        </is>
+      <c r="C4" t="n">
+        <v>126062</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -677,8 +678,75 @@
           <t>ID_20260505144724</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA LA CIMA, C.A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0000003384</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hector A. Hernandez</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NO PERTENECEN A LA RECEPCION ADOBO COMPLETO 125G, CANELA MOLIDA MC CORMICK 60 GRS,PIMENTON ESPANOL MC CORMICK 65 GRS</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ID_20260506144634</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/IPSFA.xlsx
+++ b/cuadros/MAYO/IPSFA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -691,10 +691,8 @@
           <t>COMERCIALIZADORA LA CIMA, C.A</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0000003384</t>
-        </is>
+      <c r="C5" t="n">
+        <v>3384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -745,6 +743,72 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROCESADORA DE VEGETALES Y FRUTAS PROVEFRU, C.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>021815</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Elys J. Bolivar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>FALTO POR FISCALIZAR LA HIERBABUENA, SE COLOCO OTRO en vez del correspondiente, SKU AJI DULCE repetido</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260507072458</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/IPSFA.xlsx
+++ b/cuadros/MAYO/IPSFA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -755,10 +755,8 @@
           <t>PROCESADORA DE VEGETALES Y FRUTAS PROVEFRU, C.A.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>021815</t>
-        </is>
+      <c r="C6" t="n">
+        <v>21815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -809,6 +807,72 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA BARCO PESCA,C.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>244543</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jose G. Maurel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>FALTANTE DE 800 GR DE RONCADOR, SE RECIBEN 65.2KG Y LA FACTURA INDICA 66KG</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ID_20260507120416</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/IPSFA.xlsx
+++ b/cuadros/MAYO/IPSFA.xlsx
@@ -752,11 +752,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PROCESADORA DE VEGETALES Y FRUTAS PROVEFRU, C.A.</t>
+          <t>DISTRIBUIDORA BARCO PESCA,C.A.</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21815</v>
+        <v>244543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -770,12 +770,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Elys J. Bolivar</t>
+          <t>Jose G. Maurel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
+          <t>ERROR DE KG EN TARA.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FALTO POR FISCALIZAR LA HIERBABUENA, SE COLOCO OTRO en vez del correspondiente, SKU AJI DULCE repetido</t>
+          <t>SE COLOCO LA TARA EN 2.4KG CUANDO LA CESTAS SON DE 2.2KG</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -803,7 +803,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260507072458</t>
+          <t>ID_20260507120416</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -816,12 +816,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA BARCO PESCA,C.A.</t>
+          <t>PROCESADORA DE VEGETALES Y FRUTAS PROVEFRU, C.A.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>244543</t>
+          <t>21815</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -836,22 +836,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jose G. Maurel</t>
+          <t>Elys J. Bolivar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TIPO D</t>
+          <t>TIPO C</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FALTANTE DE 800 GR DE RONCADOR, SE RECIBEN 65.2KG Y LA FACTURA INDICA 66KG</t>
+          <t>FALTO POR FISCALIZAR LA HIERBABUENA, SE COLOCO OTRO SKU EN VEZ DEL CORRESPONDIENTE, SKU AJI DULCE repetido</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ID_20260507120416</t>
+          <t>ID_20260507072458</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>

--- a/cuadros/MAYO/IPSFA.xlsx
+++ b/cuadros/MAYO/IPSFA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,10 +819,8 @@
           <t>PROCESADORA DE VEGETALES Y FRUTAS PROVEFRU, C.A.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>21815</t>
-        </is>
+      <c r="C7" t="n">
+        <v>21815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -873,6 +871,72 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MUSACEUM C.A</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>004258</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>JOSE MAUREL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NO SE TERMINO EL PROCESO EN EL TIEMPO ESTABLECIDO</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ID_20260507134415</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/IPSFA.xlsx
+++ b/cuadros/MAYO/IPSFA.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,10 +939,8 @@
           <t>INVERSIONES LAS PATRONAS 2024, C.A</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>000619</t>
-        </is>
+      <c r="C9" t="n">
+        <v>619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -990,6 +988,71 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>ID_20260508124240</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>INVERSIONES AGROPECUARIA JEANDAVID, C.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>019304</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MIGUEL A. BLANCO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SE CARGA EL DOCUEMNTO DE LA DEVOLUCION EN LA RECEPCION</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ID_20260512121720</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/IPSFA.xlsx
+++ b/cuadros/MAYO/IPSFA.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +550,7 @@
           <t>HIST_20260504164252</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -612,6 +614,7 @@
           <t>ID_20260505142248</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -675,6 +678,7 @@
           <t>ID_20260505144724</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -738,6 +742,7 @@
           <t>ID_20260506144634</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -801,6 +806,7 @@
           <t>ID_20260507120416</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -864,6 +870,7 @@
           <t>ID_20260507072458</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -927,6 +934,7 @@
           <t>ID_20260507134415</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -990,6 +998,7 @@
           <t>ID_20260508124240</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1002,10 +1011,8 @@
           <t>INVERSIONES AGROPECUARIA JEANDAVID, C.A.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>019304</t>
-        </is>
+      <c r="C10" t="n">
+        <v>19304</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1055,8 +1062,75 @@
           <t>ID_20260512121720</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>000688</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DOUGLAS A. BUSTAMANTE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SE CARGO DOS VECES LA GUANABANA</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ID_20260513151127</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/IPSFA.xlsx
+++ b/cuadros/MAYO/IPSFA.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -499,8 +498,10 @@
           <t>YEFFERSON MAY MORGADO CHACON</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>125981</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>125981</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -550,7 +551,6 @@
           <t>HIST_20260504164252</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -563,8 +563,10 @@
           <t>CORPORACION JSL, C.A</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>40097731</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>40097731</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -614,7 +616,6 @@
           <t>ID_20260505142248</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -627,8 +628,10 @@
           <t>YEFFERSON MAY MORGADO CHACON</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>126062</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>126062</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -678,7 +681,6 @@
           <t>ID_20260505144724</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -691,8 +693,10 @@
           <t>COMERCIALIZADORA LA CIMA, C.A</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>3384</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3384</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -742,7 +746,6 @@
           <t>ID_20260506144634</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -755,8 +758,10 @@
           <t>DISTRIBUIDORA BARCO PESCA,C.A.</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>244543</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>244543</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -806,7 +811,6 @@
           <t>ID_20260507120416</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -819,8 +823,10 @@
           <t>PROCESADORA DE VEGETALES Y FRUTAS PROVEFRU, C.A.</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>21815</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>21815</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -870,7 +876,6 @@
           <t>ID_20260507072458</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -883,8 +888,10 @@
           <t>MUSACEUM C.A</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>4258</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4258</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -934,7 +941,6 @@
           <t>ID_20260507134415</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -947,8 +953,10 @@
           <t>INVERSIONES LAS PATRONAS 2024, C.A</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>619</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -998,7 +1006,6 @@
           <t>ID_20260508124240</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1011,8 +1018,10 @@
           <t>INVERSIONES AGROPECUARIA JEANDAVID, C.A.</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>19304</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19304</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1062,7 +1071,6 @@
           <t>ID_20260512121720</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1128,9 +1136,8 @@
           <t>ID_20260513151127</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/IPSFA.xlsx
+++ b/cuadros/MAYO/IPSFA.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1134,6 +1134,76 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>ID_20260513151127</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MUSACEUM C.A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>004392</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>HECTOR A. HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NO SE TERMINA EL PROCESO EN EL TIEMPO ESTABLECIDO</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ID_20260515153352</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>INC_153352_0.png</t>
         </is>
       </c>
     </row>
